--- a/outputs/list_ies_final.xlsx
+++ b/outputs/list_ies_final.xlsx
@@ -2715,12 +2715,24 @@
         <v>129</v>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de Teófilo Otoni</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2741,24 @@
         <v>130</v>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Faculdade de Administracao de Teofilo Otoni</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -5401,12 +5425,24 @@
         <v>290</v>
       </c>
       <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de Joinville</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5451,24 @@
         <v>291</v>
       </c>
       <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Faculdade de Psicologia de Joinville</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -5548,13 +5596,29 @@
       <c r="A174" t="n">
         <v>297</v>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>FCCASJT</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Contábeis e Administrativas São Judas Tadeu</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -6908,13 +6972,21 @@
       <c r="A220" t="n">
         <v>390</v>
       </c>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>FATE</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Faculdade Ateneu</t>
+        </is>
+      </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7355,24 @@
         <v>413</v>
       </c>
       <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Faculdade Porto-Alegrense de Educacao, Ciencias e</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7381,24 @@
         <v>414</v>
       </c>
       <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Faculdade Porto-Alegrense de Ciencias Contabeis e Administrativas</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -8510,13 +8606,29 @@
       <c r="A275" t="n">
         <v>470</v>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>FONF</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Faculdade de Odontologia de Nova Friburgo</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -8765,12 +8877,24 @@
         <v>487</v>
       </c>
       <c r="B284" t="inlineStr"/>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Faculdade de Administração, Ciências Contábeis, Jurídicas e Sociais do Estado de</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>PÚBLICA ESTADUAL</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -9048,13 +9172,21 @@
       <c r="A294" t="n">
         <v>498</v>
       </c>
-      <c r="B294" t="inlineStr"/>
-      <c r="C294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>FAR</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Faculdade Adelmar Rosado</t>
+        </is>
+      </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -9063,12 +9195,24 @@
         <v>499</v>
       </c>
       <c r="B295" t="inlineStr"/>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito e Administracao Catanduva</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -9076,13 +9220,21 @@
       <c r="A296" t="n">
         <v>500</v>
       </c>
-      <c r="B296" t="inlineStr"/>
-      <c r="C296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Universidade Presidente Antonio Carlos</t>
+        </is>
+      </c>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -9600,13 +9752,29 @@
       <c r="A314" t="n">
         <v>524</v>
       </c>
-      <c r="B314" t="inlineStr"/>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>FAFIOF</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Faculdade de Filosofia Ciências e Letras de Ouro Fino</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -11744,13 +11912,29 @@
       <c r="A386" t="n">
         <v>632</v>
       </c>
-      <c r="B386" t="inlineStr"/>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>FACEAC</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Econômicas, Administrativas e Contábeis de São Sebastião D</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -12778,13 +12962,29 @@
       <c r="A421" t="n">
         <v>678</v>
       </c>
-      <c r="B421" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>FOPLAC</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Faculdade de Odontologia do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -12792,13 +12992,29 @@
       <c r="A422" t="n">
         <v>679</v>
       </c>
-      <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>FARPLAC</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Faculdade de Reabilitação do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -12987,12 +13203,24 @@
         <v>690</v>
       </c>
       <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
-      <c r="E429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Contabeis e Administrativas de Taquara</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -13960,13 +14188,29 @@
       <c r="A462" t="n">
         <v>729</v>
       </c>
-      <c r="B462" t="inlineStr"/>
-      <c r="C462" t="inlineStr"/>
-      <c r="D462" t="inlineStr"/>
-      <c r="E462" t="inlineStr"/>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>FAFIPREVE</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Faculdade de Filosofia Ciências e Letras de Presidente Venceslau</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -15680,13 +15924,21 @@
       <c r="A520" t="n">
         <v>819</v>
       </c>
-      <c r="B520" t="inlineStr"/>
-      <c r="C520" t="inlineStr"/>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>CESMAC</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Centro de Estudos Superiores de Maceio</t>
+        </is>
+      </c>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -16564,13 +16816,29 @@
       <c r="A550" t="n">
         <v>875</v>
       </c>
-      <c r="B550" t="inlineStr"/>
-      <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
-      <c r="E550" t="inlineStr"/>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>FESB</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Faculdade de Estudos Sociais de Barra do Garças</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -16578,13 +16846,29 @@
       <c r="A551" t="n">
         <v>876</v>
       </c>
-      <c r="B551" t="inlineStr"/>
-      <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>FATEV</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Faculdade de Tecnologia do Vale do Araguaia</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -18261,12 +18545,24 @@
         <v>1015</v>
       </c>
       <c r="B608" t="inlineStr"/>
-      <c r="C608" t="inlineStr"/>
-      <c r="D608" t="inlineStr"/>
-      <c r="E608" t="inlineStr"/>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Contábeis Machado de Assis</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -19230,13 +19526,29 @@
       <c r="A641" t="n">
         <v>1069</v>
       </c>
-      <c r="B641" t="inlineStr"/>
-      <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
-      <c r="E641" t="inlineStr"/>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>CRECIH</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Centro Regional de Estudos em Ciencias Humanas</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -19695,12 +20007,24 @@
         <v>1088</v>
       </c>
       <c r="B657" t="inlineStr"/>
-      <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
-      <c r="E657" t="inlineStr"/>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Faculdade de Desenho Industrial de Joinville</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -19768,13 +20092,29 @@
       <c r="A660" t="n">
         <v>1091</v>
       </c>
-      <c r="B660" t="inlineStr"/>
-      <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
-      <c r="E660" t="inlineStr"/>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>FPVGP</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Faculdade de Pedagogia de Vargem Grande Paulista</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -20768,13 +21108,29 @@
       <c r="A694" t="n">
         <v>1145</v>
       </c>
-      <c r="B694" t="inlineStr"/>
-      <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
-      <c r="E694" t="inlineStr"/>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>AGROPLAC</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Agrárias do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -21623,12 +21979,24 @@
         <v>1197</v>
       </c>
       <c r="B723" t="inlineStr"/>
-      <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
-      <c r="E723" t="inlineStr"/>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Faculdade de Turismo - Aema/Rj</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -21757,12 +22125,24 @@
         <v>1203</v>
       </c>
       <c r="B728" t="inlineStr"/>
-      <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
-      <c r="E728" t="inlineStr"/>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Faculdade de Economia de Ouro Fino</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -21861,12 +22241,24 @@
         <v>1207</v>
       </c>
       <c r="B732" t="inlineStr"/>
-      <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr"/>
-      <c r="E732" t="inlineStr"/>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Faculdade de Administracao Geral</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -21901,12 +22293,24 @@
         <v>1210</v>
       </c>
       <c r="B734" t="inlineStr"/>
-      <c r="C734" t="inlineStr"/>
-      <c r="D734" t="inlineStr"/>
-      <c r="E734" t="inlineStr"/>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias da Comunicacao de Taquara</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -22035,12 +22439,24 @@
         <v>1223</v>
       </c>
       <c r="B739" t="inlineStr"/>
-      <c r="C739" t="inlineStr"/>
-      <c r="D739" t="inlineStr"/>
-      <c r="E739" t="inlineStr"/>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Faculdade Radial Jabaquara</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -22409,12 +22825,24 @@
         <v>1238</v>
       </c>
       <c r="B752" t="inlineStr"/>
-      <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
-      <c r="E752" t="inlineStr"/>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Contábeis do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -22903,12 +23331,24 @@
         <v>1259</v>
       </c>
       <c r="B769" t="inlineStr"/>
-      <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Faculdade Nobel</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -23216,13 +23656,29 @@
       <c r="A780" t="n">
         <v>1278</v>
       </c>
-      <c r="B780" t="inlineStr"/>
-      <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr"/>
-      <c r="E780" t="inlineStr"/>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>FAECH</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Faculdade Adventista de Educação e Ciências Humanas</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23807,24 @@
         <v>1287</v>
       </c>
       <c r="B785" t="inlineStr"/>
-      <c r="C785" t="inlineStr"/>
-      <c r="D785" t="inlineStr"/>
-      <c r="E785" t="inlineStr"/>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Gerenciais do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -24827,12 +25295,24 @@
         <v>1348</v>
       </c>
       <c r="B835" t="inlineStr"/>
-      <c r="C835" t="inlineStr"/>
-      <c r="D835" t="inlineStr"/>
-      <c r="E835" t="inlineStr"/>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Faculdade Batista de Administracao e Informatica</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -24900,13 +25380,29 @@
       <c r="A838" t="n">
         <v>1352</v>
       </c>
-      <c r="B838" t="inlineStr"/>
-      <c r="C838" t="inlineStr"/>
-      <c r="D838" t="inlineStr"/>
-      <c r="E838" t="inlineStr"/>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>FAEF</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Faculdade Adventista de Educação Física</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -25424,13 +25920,25 @@
       <c r="A856" t="n">
         <v>1380</v>
       </c>
-      <c r="B856" t="inlineStr"/>
-      <c r="C856" t="inlineStr"/>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>URSES</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Faculdade de Domingos Martins</t>
+        </is>
+      </c>
       <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -27680,13 +28188,21 @@
       <c r="A932" t="n">
         <v>1485</v>
       </c>
-      <c r="B932" t="inlineStr"/>
-      <c r="C932" t="inlineStr"/>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>FASERT</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Faculdade de Sertaozinho</t>
+        </is>
+      </c>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr"/>
       <c r="F932" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -28534,13 +29050,29 @@
       <c r="A961" t="n">
         <v>1517</v>
       </c>
-      <c r="B961" t="inlineStr"/>
-      <c r="C961" t="inlineStr"/>
-      <c r="D961" t="inlineStr"/>
-      <c r="E961" t="inlineStr"/>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Faculdade Novo Ateneu de Guarapuava</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -28814,13 +29346,29 @@
       <c r="A971" t="n">
         <v>1531</v>
       </c>
-      <c r="B971" t="inlineStr"/>
-      <c r="C971" t="inlineStr"/>
-      <c r="D971" t="inlineStr"/>
-      <c r="E971" t="inlineStr"/>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>FENPLAC</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Faculdade de Enfermagem do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -29361,12 +29909,24 @@
         <v>1555</v>
       </c>
       <c r="B990" t="inlineStr"/>
-      <c r="C990" t="inlineStr"/>
-      <c r="D990" t="inlineStr"/>
-      <c r="E990" t="inlineStr"/>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de Guarapuava</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -31106,13 +31666,29 @@
       <c r="A1049" t="n">
         <v>1626</v>
       </c>
-      <c r="B1049" t="inlineStr"/>
-      <c r="C1049" t="inlineStr"/>
-      <c r="D1049" t="inlineStr"/>
-      <c r="E1049" t="inlineStr"/>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>ETEP</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Centro de Tecnologia e Ciência - Cetec</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -31180,13 +31756,21 @@
       <c r="A1052" t="n">
         <v>1631</v>
       </c>
-      <c r="B1052" t="inlineStr"/>
-      <c r="C1052" t="inlineStr"/>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>URCAMP</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Universidade da Regiao da Campanha</t>
+        </is>
+      </c>
       <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr"/>
       <c r="F1052" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -32592,13 +33176,29 @@
       <c r="A1100" t="n">
         <v>1684</v>
       </c>
-      <c r="B1100" t="inlineStr"/>
-      <c r="C1100" t="inlineStr"/>
-      <c r="D1100" t="inlineStr"/>
-      <c r="E1100" t="inlineStr"/>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>FASES</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Faculdade de Roraima</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -32662,13 +33262,29 @@
       <c r="A1103" t="n">
         <v>1687</v>
       </c>
-      <c r="B1103" t="inlineStr"/>
-      <c r="C1103" t="inlineStr"/>
-      <c r="D1103" t="inlineStr"/>
-      <c r="E1103" t="inlineStr"/>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>IDEPE</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Faculdade Idepe</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -32947,12 +33563,24 @@
         <v>1698</v>
       </c>
       <c r="B1113" t="inlineStr"/>
-      <c r="C1113" t="inlineStr"/>
-      <c r="D1113" t="inlineStr"/>
-      <c r="E1113" t="inlineStr"/>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Sociais Aplicadas do Cescare</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -34187,12 +34815,24 @@
         <v>1751</v>
       </c>
       <c r="B1155" t="inlineStr"/>
-      <c r="C1155" t="inlineStr"/>
-      <c r="D1155" t="inlineStr"/>
-      <c r="E1155" t="inlineStr"/>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Faculdade de Design Grafico</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -34260,13 +34900,29 @@
       <c r="A1158" t="n">
         <v>1754</v>
       </c>
-      <c r="B1158" t="inlineStr"/>
-      <c r="C1158" t="inlineStr"/>
-      <c r="D1158" t="inlineStr"/>
-      <c r="E1158" t="inlineStr"/>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>FACGAMA</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educação de Brasília</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -34810,13 +35466,29 @@
       <c r="A1177" t="n">
         <v>1778</v>
       </c>
-      <c r="B1177" t="inlineStr"/>
-      <c r="C1177" t="inlineStr"/>
-      <c r="D1177" t="inlineStr"/>
-      <c r="E1177" t="inlineStr"/>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>FECLSJT</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Faculdade de Educação, Ciências e Letras São Judas Tadeu</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -35322,13 +35994,29 @@
       <c r="A1195" t="n">
         <v>1799</v>
       </c>
-      <c r="B1195" t="inlineStr"/>
-      <c r="C1195" t="inlineStr"/>
-      <c r="D1195" t="inlineStr"/>
-      <c r="E1195" t="inlineStr"/>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>FACULDADE BRASÍLIA</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Faculdade Brasília de Tecnologia, Ciências e Educação</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1195" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -36117,12 +36805,24 @@
         <v>1826</v>
       </c>
       <c r="B1222" t="inlineStr"/>
-      <c r="C1222" t="inlineStr"/>
-      <c r="D1222" t="inlineStr"/>
-      <c r="E1222" t="inlineStr"/>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de Leopoldina</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1222" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -37030,13 +37730,29 @@
       <c r="A1253" t="n">
         <v>1859</v>
       </c>
-      <c r="B1253" t="inlineStr"/>
-      <c r="C1253" t="inlineStr"/>
-      <c r="D1253" t="inlineStr"/>
-      <c r="E1253" t="inlineStr"/>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>FACILUZ</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao Uirapuru</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1253" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -37850,13 +38566,29 @@
       <c r="A1281" t="n">
         <v>1889</v>
       </c>
-      <c r="B1281" t="inlineStr"/>
-      <c r="C1281" t="inlineStr"/>
-      <c r="D1281" t="inlineStr"/>
-      <c r="E1281" t="inlineStr"/>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>FAHL</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Faculdade Hoyler de Letras</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1281" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -38461,12 +39193,24 @@
         <v>1912</v>
       </c>
       <c r="B1302" t="inlineStr"/>
-      <c r="C1302" t="inlineStr"/>
-      <c r="D1302" t="inlineStr"/>
-      <c r="E1302" t="inlineStr"/>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao Japi</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1302" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -38504,13 +39248,21 @@
       <c r="A1304" t="n">
         <v>1914</v>
       </c>
-      <c r="B1304" t="inlineStr"/>
-      <c r="C1304" t="inlineStr"/>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Faculdade do Tapajos</t>
+        </is>
+      </c>
       <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="inlineStr"/>
       <c r="F1304" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -38638,13 +39390,29 @@
       <c r="A1309" t="n">
         <v>1920</v>
       </c>
-      <c r="B1309" t="inlineStr"/>
-      <c r="C1309" t="inlineStr"/>
-      <c r="D1309" t="inlineStr"/>
-      <c r="E1309" t="inlineStr"/>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>FARMPLAC</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Faculdade de Farmácia do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1309" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -38833,12 +39601,24 @@
         <v>1929</v>
       </c>
       <c r="B1316" t="inlineStr"/>
-      <c r="C1316" t="inlineStr"/>
-      <c r="D1316" t="inlineStr"/>
-      <c r="E1316" t="inlineStr"/>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Contábeis - Facicont</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1316" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -39438,13 +40218,29 @@
       <c r="A1337" t="n">
         <v>1953</v>
       </c>
-      <c r="B1337" t="inlineStr"/>
-      <c r="C1337" t="inlineStr"/>
-      <c r="D1337" t="inlineStr"/>
-      <c r="E1337" t="inlineStr"/>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>FACBIOS</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Biológicas e da Saúde</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1337" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -39453,12 +40249,24 @@
         <v>1954</v>
       </c>
       <c r="B1338" t="inlineStr"/>
-      <c r="C1338" t="inlineStr"/>
-      <c r="D1338" t="inlineStr"/>
-      <c r="E1338" t="inlineStr"/>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Faculdade de Economia</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1338" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -39557,12 +40365,24 @@
         <v>1959</v>
       </c>
       <c r="B1342" t="inlineStr"/>
-      <c r="C1342" t="inlineStr"/>
-      <c r="D1342" t="inlineStr"/>
-      <c r="E1342" t="inlineStr"/>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Jurídicas do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1342" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -39570,13 +40390,29 @@
       <c r="A1343" t="n">
         <v>1960</v>
       </c>
-      <c r="B1343" t="inlineStr"/>
-      <c r="C1343" t="inlineStr"/>
-      <c r="D1343" t="inlineStr"/>
-      <c r="E1343" t="inlineStr"/>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>FAMEPLAC</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Faculdade de Medicina do Planalto Central</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1343" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -40120,13 +40956,29 @@
       <c r="A1362" t="n">
         <v>1985</v>
       </c>
-      <c r="B1362" t="inlineStr"/>
-      <c r="C1362" t="inlineStr"/>
-      <c r="D1362" t="inlineStr"/>
-      <c r="E1362" t="inlineStr"/>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>FAC</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Faculdade Comunitária de Campinas</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1362" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -40255,12 +41107,24 @@
         <v>1990</v>
       </c>
       <c r="B1367" t="inlineStr"/>
-      <c r="C1367" t="inlineStr"/>
-      <c r="D1367" t="inlineStr"/>
-      <c r="E1367" t="inlineStr"/>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Sociais Aplicadas de Fortaleza</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1367" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -41285,12 +42149,24 @@
         <v>2046</v>
       </c>
       <c r="B1402" t="inlineStr"/>
-      <c r="C1402" t="inlineStr"/>
-      <c r="D1402" t="inlineStr"/>
-      <c r="E1402" t="inlineStr"/>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao Amadeus</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -41329,12 +42205,24 @@
         <v>2052</v>
       </c>
       <c r="B1404" t="inlineStr"/>
-      <c r="C1404" t="inlineStr"/>
-      <c r="D1404" t="inlineStr"/>
-      <c r="E1404" t="inlineStr"/>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de Lages</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -42213,12 +43101,24 @@
         <v>2127</v>
       </c>
       <c r="B1434" t="inlineStr"/>
-      <c r="C1434" t="inlineStr"/>
-      <c r="D1434" t="inlineStr"/>
-      <c r="E1434" t="inlineStr"/>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Faculdade Batista de Educacao</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -42796,13 +43696,29 @@
       <c r="A1454" t="n">
         <v>2155</v>
       </c>
-      <c r="B1454" t="inlineStr"/>
-      <c r="C1454" t="inlineStr"/>
-      <c r="D1454" t="inlineStr"/>
-      <c r="E1454" t="inlineStr"/>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Faculdades Doctum</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Sociais e da Saúde de Cataguases</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -43646,13 +44562,29 @@
       <c r="A1483" t="n">
         <v>2211</v>
       </c>
-      <c r="B1483" t="inlineStr"/>
-      <c r="C1483" t="inlineStr"/>
-      <c r="D1483" t="inlineStr"/>
-      <c r="E1483" t="inlineStr"/>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>ISEF</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educação Cenecista de Farroupilha</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1483" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -43661,12 +44593,24 @@
         <v>2213</v>
       </c>
       <c r="B1484" t="inlineStr"/>
-      <c r="C1484" t="inlineStr"/>
-      <c r="D1484" t="inlineStr"/>
-      <c r="E1484" t="inlineStr"/>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Jurídicas e Sociais de Guarapari</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1484" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -43675,12 +44619,24 @@
         <v>2216</v>
       </c>
       <c r="B1485" t="inlineStr"/>
-      <c r="C1485" t="inlineStr"/>
-      <c r="D1485" t="inlineStr"/>
-      <c r="E1485" t="inlineStr"/>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao de Iuna</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1485" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -43689,12 +44645,24 @@
         <v>2217</v>
       </c>
       <c r="B1486" t="inlineStr"/>
-      <c r="C1486" t="inlineStr"/>
-      <c r="D1486" t="inlineStr"/>
-      <c r="E1486" t="inlineStr"/>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Gerenciais de Iuna</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1486" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -43762,13 +44730,29 @@
       <c r="A1489" t="n">
         <v>2223</v>
       </c>
-      <c r="B1489" t="inlineStr"/>
-      <c r="C1489" t="inlineStr"/>
-      <c r="D1489" t="inlineStr"/>
-      <c r="E1489" t="inlineStr"/>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Faculdades Doctum</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Sociais e da Saúde de Teófilo Otoni</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1489" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -44317,12 +45301,24 @@
         <v>2261</v>
       </c>
       <c r="B1508" t="inlineStr"/>
-      <c r="C1508" t="inlineStr"/>
-      <c r="D1508" t="inlineStr"/>
-      <c r="E1508" t="inlineStr"/>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Humanas e da Saúde de Taquara</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1508" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -44361,12 +45357,24 @@
         <v>2265</v>
       </c>
       <c r="B1510" t="inlineStr"/>
-      <c r="C1510" t="inlineStr"/>
-      <c r="D1510" t="inlineStr"/>
-      <c r="E1510" t="inlineStr"/>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Sociais e Aplicadas</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1510" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -44465,12 +45473,24 @@
         <v>2272</v>
       </c>
       <c r="B1514" t="inlineStr"/>
-      <c r="C1514" t="inlineStr"/>
-      <c r="D1514" t="inlineStr"/>
-      <c r="E1514" t="inlineStr"/>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Faculdade de Psicologia de Lages</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1514" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -44718,13 +45738,29 @@
       <c r="A1523" t="n">
         <v>2293</v>
       </c>
-      <c r="B1523" t="inlineStr"/>
-      <c r="C1523" t="inlineStr"/>
-      <c r="D1523" t="inlineStr"/>
-      <c r="E1523" t="inlineStr"/>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>FCHBS</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Humanas, Biológicas e da Saúde</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -44883,12 +45919,24 @@
         <v>2305</v>
       </c>
       <c r="B1529" t="inlineStr"/>
-      <c r="C1529" t="inlineStr"/>
-      <c r="D1529" t="inlineStr"/>
-      <c r="E1529" t="inlineStr"/>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de Patos</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1529" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -45016,13 +46064,29 @@
       <c r="A1534" t="n">
         <v>2315</v>
       </c>
-      <c r="B1534" t="inlineStr"/>
-      <c r="C1534" t="inlineStr"/>
-      <c r="D1534" t="inlineStr"/>
-      <c r="E1534" t="inlineStr"/>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Faculdade Cearense</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1534" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -45030,13 +46094,29 @@
       <c r="A1535" t="n">
         <v>2316</v>
       </c>
-      <c r="B1535" t="inlineStr"/>
-      <c r="C1535" t="inlineStr"/>
-      <c r="D1535" t="inlineStr"/>
-      <c r="E1535" t="inlineStr"/>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>INDES</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Instituto Nacional de Desenvolvimento do Ensino Superior</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>INSTITUTO SUPERIOR OU ESCOLA SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1535" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -45494,13 +46574,29 @@
       <c r="A1551" t="n">
         <v>2345</v>
       </c>
-      <c r="B1551" t="inlineStr"/>
-      <c r="C1551" t="inlineStr"/>
-      <c r="D1551" t="inlineStr"/>
-      <c r="E1551" t="inlineStr"/>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>FASS</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>Faculdade Sete de Setembro</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1551" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -45629,12 +46725,24 @@
         <v>2353</v>
       </c>
       <c r="B1556" t="inlineStr"/>
-      <c r="C1556" t="inlineStr"/>
-      <c r="D1556" t="inlineStr"/>
-      <c r="E1556" t="inlineStr"/>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Faculdade de Administracao do Centro Educacional de Santos</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1556" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -46445,12 +47553,24 @@
         <v>2417</v>
       </c>
       <c r="B1584" t="inlineStr"/>
-      <c r="C1584" t="inlineStr"/>
-      <c r="D1584" t="inlineStr"/>
-      <c r="E1584" t="inlineStr"/>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao Metropolitano de Br</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1584" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -47955,12 +49075,24 @@
         <v>2512</v>
       </c>
       <c r="B1635" t="inlineStr"/>
-      <c r="C1635" t="inlineStr"/>
-      <c r="D1635" t="inlineStr"/>
-      <c r="E1635" t="inlineStr"/>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao Cuiabano</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1635" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -49190,13 +50322,29 @@
       <c r="A1677" t="n">
         <v>2612</v>
       </c>
-      <c r="B1677" t="inlineStr"/>
-      <c r="C1677" t="inlineStr"/>
-      <c r="D1677" t="inlineStr"/>
-      <c r="E1677" t="inlineStr"/>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>ISEMOC</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educação Montes Claros</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1677" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -49981,12 +51129,24 @@
         <v>2684</v>
       </c>
       <c r="B1704" t="inlineStr"/>
-      <c r="C1704" t="inlineStr"/>
-      <c r="D1704" t="inlineStr"/>
-      <c r="E1704" t="inlineStr"/>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Gerenciais de Leopoldina</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1704" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -50324,13 +51484,29 @@
       <c r="A1716" t="n">
         <v>2734</v>
       </c>
-      <c r="B1716" t="inlineStr"/>
-      <c r="C1716" t="inlineStr"/>
-      <c r="D1716" t="inlineStr"/>
-      <c r="E1716" t="inlineStr"/>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Faculdades Doctum</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências da Saúde de Guarapari</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1716" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -50369,12 +51545,24 @@
         <v>2738</v>
       </c>
       <c r="B1718" t="inlineStr"/>
-      <c r="C1718" t="inlineStr"/>
-      <c r="D1718" t="inlineStr"/>
-      <c r="E1718" t="inlineStr"/>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao de Guarapari</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1718" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -50712,13 +51900,29 @@
       <c r="A1730" t="n">
         <v>2764</v>
       </c>
-      <c r="B1730" t="inlineStr"/>
-      <c r="C1730" t="inlineStr"/>
-      <c r="D1730" t="inlineStr"/>
-      <c r="E1730" t="inlineStr"/>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>IESOF</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>Instituto de Ensino Superior de Ouro Fino</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>INSTITUTO SUPERIOR OU ESCOLA SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1730" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -52086,13 +53290,25 @@
       <c r="A1777" t="n">
         <v>2873</v>
       </c>
-      <c r="B1777" t="inlineStr"/>
-      <c r="C1777" t="inlineStr"/>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>SISTEMAS</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>Faculdade de Sistemas de Informação de São Sebastião do Paraíso</t>
+        </is>
+      </c>
       <c r="D1777" t="inlineStr"/>
-      <c r="E1777" t="inlineStr"/>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1777" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -52100,13 +53316,29 @@
       <c r="A1778" t="n">
         <v>2874</v>
       </c>
-      <c r="B1778" t="inlineStr"/>
-      <c r="C1778" t="inlineStr"/>
-      <c r="D1778" t="inlineStr"/>
-      <c r="E1778" t="inlineStr"/>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>DIREITO</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito de São Sebastião do Paraíso</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1778" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -52294,13 +53526,29 @@
       <c r="A1785" t="n">
         <v>2900</v>
       </c>
-      <c r="B1785" t="inlineStr"/>
-      <c r="C1785" t="inlineStr"/>
-      <c r="D1785" t="inlineStr"/>
-      <c r="E1785" t="inlineStr"/>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>INTER</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>Instituto Tecnológico Regional</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1785" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -53590,13 +54838,29 @@
       <c r="A1829" t="n">
         <v>3145</v>
       </c>
-      <c r="B1829" t="inlineStr"/>
-      <c r="C1829" t="inlineStr"/>
-      <c r="D1829" t="inlineStr"/>
-      <c r="E1829" t="inlineStr"/>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>SJT</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>Faculdade de Direito São Judas Tadeu de Porto Alegre</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1829" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -54317,12 +55581,24 @@
         <v>3174</v>
       </c>
       <c r="B1854" t="inlineStr"/>
-      <c r="C1854" t="inlineStr"/>
-      <c r="D1854" t="inlineStr"/>
-      <c r="E1854" t="inlineStr"/>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao de Vinhedo</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1854" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -54331,12 +55607,24 @@
         <v>3175</v>
       </c>
       <c r="B1855" t="inlineStr"/>
-      <c r="C1855" t="inlineStr"/>
-      <c r="D1855" t="inlineStr"/>
-      <c r="E1855" t="inlineStr"/>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao de Taquara</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1855" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -55412,13 +56700,29 @@
       <c r="A1892" t="n">
         <v>3282</v>
       </c>
-      <c r="B1892" t="inlineStr"/>
-      <c r="C1892" t="inlineStr"/>
-      <c r="D1892" t="inlineStr"/>
-      <c r="E1892" t="inlineStr"/>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>FAC PONTAL</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>Faculdade Pontal do Paranapanema</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1892" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -55516,13 +56820,29 @@
       <c r="A1896" t="n">
         <v>3298</v>
       </c>
-      <c r="B1896" t="inlineStr"/>
-      <c r="C1896" t="inlineStr"/>
-      <c r="D1896" t="inlineStr"/>
-      <c r="E1896" t="inlineStr"/>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>FATEC</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>Faculdade de Tecnologia Camões</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>FACULDADE DE TECNOLOGIA</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1896" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -57528,13 +58848,29 @@
       <c r="A1964" t="n">
         <v>3473</v>
       </c>
-      <c r="B1964" t="inlineStr"/>
-      <c r="C1964" t="inlineStr"/>
-      <c r="D1964" t="inlineStr"/>
-      <c r="E1964" t="inlineStr"/>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>FAVALE</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>Faculdade de Filosofia, Ciências e Letras de Carangola</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1964" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -57542,13 +58878,29 @@
       <c r="A1965" t="n">
         <v>3474</v>
       </c>
-      <c r="B1965" t="inlineStr"/>
-      <c r="C1965" t="inlineStr"/>
-      <c r="D1965" t="inlineStr"/>
-      <c r="E1965" t="inlineStr"/>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>FAVALE</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Exatas</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F1965" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -58847,12 +60199,24 @@
         <v>3594</v>
       </c>
       <c r="B2009" t="inlineStr"/>
-      <c r="C2009" t="inlineStr"/>
-      <c r="D2009" t="inlineStr"/>
-      <c r="E2009" t="inlineStr"/>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencia, Tecnologia e Educacao</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2009" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -58976,13 +60340,29 @@
       <c r="A2014" t="n">
         <v>3606</v>
       </c>
-      <c r="B2014" t="inlineStr"/>
-      <c r="C2014" t="inlineStr"/>
-      <c r="D2014" t="inlineStr"/>
-      <c r="E2014" t="inlineStr"/>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>ISEP</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao Presbiteriano Vale</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2014" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -59021,12 +60401,24 @@
         <v>3608</v>
       </c>
       <c r="B2016" t="inlineStr"/>
-      <c r="C2016" t="inlineStr"/>
-      <c r="D2016" t="inlineStr"/>
-      <c r="E2016" t="inlineStr"/>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>Instituto Superior de Educacao de Londrina</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2016" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -60021,12 +61413,24 @@
         <v>3701</v>
       </c>
       <c r="B2050" t="inlineStr"/>
-      <c r="C2050" t="inlineStr"/>
-      <c r="D2050" t="inlineStr"/>
-      <c r="E2050" t="inlineStr"/>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciencias Gerenciais de Teofilo Otoni</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>CENTRO UNIVERSITÁRIO</t>
+        </is>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2050" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -61016,13 +62420,29 @@
       <c r="A2084" t="n">
         <v>3791</v>
       </c>
-      <c r="B2084" t="inlineStr"/>
-      <c r="C2084" t="inlineStr"/>
-      <c r="D2084" t="inlineStr"/>
-      <c r="E2084" t="inlineStr"/>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>FAMEVAÇO</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>Faculdade de Medicina do Vale do Aço</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2084" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -61382,13 +62802,21 @@
       <c r="A2097" t="n">
         <v>3832</v>
       </c>
-      <c r="B2097" t="inlineStr"/>
-      <c r="C2097" t="inlineStr"/>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>UNIBAN</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>Universidade Bandeirante de São Paulo</t>
+        </is>
+      </c>
       <c r="D2097" t="inlineStr"/>
       <c r="E2097" t="inlineStr"/>
       <c r="F2097" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -61662,13 +63090,29 @@
       <c r="A2107" t="n">
         <v>3865</v>
       </c>
-      <c r="B2107" t="inlineStr"/>
-      <c r="C2107" t="inlineStr"/>
-      <c r="D2107" t="inlineStr"/>
-      <c r="E2107" t="inlineStr"/>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>FIPH</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>Faculdades Integradas Padre Humberto</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2107" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -62538,13 +63982,29 @@
       <c r="A2137" t="n">
         <v>3971</v>
       </c>
-      <c r="B2137" t="inlineStr"/>
-      <c r="C2137" t="inlineStr"/>
-      <c r="D2137" t="inlineStr"/>
-      <c r="E2137" t="inlineStr"/>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>IESPEN</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>União Educacional de Porto Nacional - Uniporto</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>INSESCSUP</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>PÚBLICA MUNICIPAL</t>
+        </is>
+      </c>
       <c r="F2137" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -69018,13 +70478,29 @@
       <c r="A2355" t="n">
         <v>4790</v>
       </c>
-      <c r="B2355" t="inlineStr"/>
-      <c r="C2355" t="inlineStr"/>
-      <c r="D2355" t="inlineStr"/>
-      <c r="E2355" t="inlineStr"/>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>CENTEC</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>Faculdade de Tecnologia Centec - Sobral</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2355" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -69062,13 +70538,29 @@
       <c r="A2357" t="n">
         <v>4792</v>
       </c>
-      <c r="B2357" t="inlineStr"/>
-      <c r="C2357" t="inlineStr"/>
-      <c r="D2357" t="inlineStr"/>
-      <c r="E2357" t="inlineStr"/>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>CENTEC</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>Faculdade de Tecnologia Centec - Limoeiro do Norte</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>FACULDADE</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>PRIVADA</t>
+        </is>
+      </c>
       <c r="F2357" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
     </row>

--- a/outputs/list_ies_final.xlsx
+++ b/outputs/list_ies_final.xlsx
@@ -40968,7 +40968,7 @@
       </c>
       <c r="D1362" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Faculdade</t>
         </is>
       </c>
       <c r="E1362" t="inlineStr">
